--- a/Hardware-Designing/_Documents/Martin_BOM_DigiKey.xlsx
+++ b/Hardware-Designing/_Documents/Martin_BOM_DigiKey.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\Martin_Smith\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GitHub\Martin_Smith\Hardware-Designing\_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -794,14 +794,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="4">
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
     <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0.00000_ ;_-[$$-409]* \-#,##0.00000\ ;_-[$$-409]* &quot;-&quot;?????_ ;_-@_ "/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -916,8 +916,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -945,6 +952,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -1378,15 +1390,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="142">
+  <cellXfs count="143">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="2" applyBorder="1"/>
     <xf numFmtId="165" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -1416,170 +1429,380 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="2" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="25" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="2" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1591,219 +1814,11 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="8" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="25" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="165" fontId="16" fillId="6" borderId="0" xfId="3" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
     <cellStyle name="Check Cell" xfId="2" builtinId="23"/>
+    <cellStyle name="Good" xfId="3" builtinId="26"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
@@ -2117,7 +2132,7 @@
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23.42578125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="39.28515625" style="136" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="39.28515625" style="122" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="23.42578125" style="1" customWidth="1"/>
     <col min="5" max="5" width="20.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="28.42578125" style="1" bestFit="1" customWidth="1"/>
@@ -2135,180 +2150,180 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="80" t="s">
+      <c r="A1" s="129" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="81"/>
-      <c r="C1" s="82"/>
-      <c r="D1" s="82"/>
-      <c r="E1" s="82"/>
-      <c r="F1" s="82"/>
-      <c r="G1" s="82"/>
-      <c r="H1" s="82"/>
-      <c r="I1" s="82"/>
-      <c r="J1" s="82"/>
-      <c r="K1" s="82"/>
-      <c r="L1" s="82"/>
-      <c r="M1" s="82"/>
-      <c r="N1" s="82"/>
-      <c r="O1" s="110"/>
-      <c r="P1" s="103"/>
-      <c r="Q1" s="83"/>
+      <c r="B1" s="130"/>
+      <c r="C1" s="131"/>
+      <c r="D1" s="131"/>
+      <c r="E1" s="131"/>
+      <c r="F1" s="131"/>
+      <c r="G1" s="131"/>
+      <c r="H1" s="131"/>
+      <c r="I1" s="131"/>
+      <c r="J1" s="131"/>
+      <c r="K1" s="131"/>
+      <c r="L1" s="131"/>
+      <c r="M1" s="131"/>
+      <c r="N1" s="131"/>
+      <c r="O1" s="132"/>
+      <c r="P1" s="90"/>
+      <c r="Q1" s="70"/>
     </row>
     <row r="2" spans="1:17" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="85" t="s">
+      <c r="A2" s="72" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="139" t="s">
+      <c r="B2" s="125" t="s">
         <v>226</v>
       </c>
-      <c r="C2" s="85" t="s">
+      <c r="C2" s="72" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="85" t="s">
+      <c r="D2" s="72" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="85" t="s">
+      <c r="E2" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="85" t="s">
+      <c r="F2" s="72" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="85" t="s">
+      <c r="G2" s="72" t="s">
         <v>225</v>
       </c>
-      <c r="H2" s="85" t="s">
+      <c r="H2" s="72" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="85" t="s">
+      <c r="I2" s="72" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="85" t="s">
+      <c r="J2" s="72" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="85" t="s">
+      <c r="K2" s="72" t="s">
         <v>16</v>
       </c>
-      <c r="L2" s="140" t="s">
+      <c r="L2" s="126" t="s">
         <v>13</v>
       </c>
-      <c r="M2" s="85" t="s">
+      <c r="M2" s="72" t="s">
         <v>8</v>
       </c>
-      <c r="N2" s="85" t="s">
+      <c r="N2" s="72" t="s">
         <v>9</v>
       </c>
-      <c r="O2" s="85" t="s">
+      <c r="O2" s="72" t="s">
         <v>17</v>
       </c>
-      <c r="P2" s="84" t="s">
+      <c r="P2" s="71" t="s">
         <v>19</v>
       </c>
-      <c r="Q2" s="85" t="s">
+      <c r="Q2" s="72" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="141">
+      <c r="A3" s="127">
         <v>1</v>
       </c>
-      <c r="B3" s="54" t="s">
+      <c r="B3" s="134" t="s">
         <v>227</v>
       </c>
-      <c r="C3" s="126" t="s">
+      <c r="C3" s="112" t="s">
         <v>28</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="D3" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="E3" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="F3" s="61" t="s">
+      <c r="F3" s="56" t="s">
         <v>142</v>
       </c>
-      <c r="G3" s="15" t="s">
+      <c r="G3" s="13" t="s">
         <v>202</v>
       </c>
-      <c r="H3" s="16" t="s">
-        <v>250</v>
-      </c>
-      <c r="I3" s="15" t="s">
+      <c r="H3" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="I3" s="13" t="s">
         <v>175</v>
       </c>
-      <c r="J3" s="17">
+      <c r="J3" s="15">
         <v>2</v>
       </c>
-      <c r="K3" s="18">
+      <c r="K3" s="16">
         <f>J3*5</f>
         <v>10</v>
       </c>
-      <c r="L3" s="41" t="s">
+      <c r="L3" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="M3" s="19">
+      <c r="M3" s="17">
         <v>0.1</v>
       </c>
-      <c r="N3" s="20">
+      <c r="N3" s="18">
         <f>J3*M3</f>
         <v>0.2</v>
       </c>
-      <c r="O3" s="111">
+      <c r="O3" s="97">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="P3" s="104">
+      <c r="P3" s="91">
         <f>O3*K3</f>
         <v>0.21000000000000002</v>
       </c>
       <c r="Q3" s="6"/>
     </row>
-    <row r="4" spans="1:17" s="53" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="141">
+    <row r="4" spans="1:17" s="51" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="127">
         <v>2</v>
       </c>
-      <c r="B4" s="55"/>
-      <c r="C4" s="127" t="s">
+      <c r="B4" s="137"/>
+      <c r="C4" s="113" t="s">
         <v>243</v>
       </c>
-      <c r="D4" s="52" t="s">
+      <c r="D4" s="50" t="s">
         <v>73</v>
       </c>
-      <c r="E4" s="52" t="s">
+      <c r="E4" s="50" t="s">
         <v>115</v>
       </c>
-      <c r="F4" s="26" t="s">
+      <c r="F4" s="24" t="s">
         <v>143</v>
       </c>
-      <c r="G4" s="52" t="s">
+      <c r="G4" s="50" t="s">
         <v>203</v>
       </c>
-      <c r="H4" s="22" t="s">
-        <v>250</v>
-      </c>
-      <c r="I4" s="52" t="s">
+      <c r="H4" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="I4" s="50" t="s">
         <v>176</v>
       </c>
-      <c r="J4" s="40">
+      <c r="J4" s="38">
         <v>6</v>
       </c>
-      <c r="K4" s="24">
+      <c r="K4" s="22">
         <f>J4*5</f>
         <v>30</v>
       </c>
-      <c r="L4" s="42" t="s">
+      <c r="L4" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="M4" s="68">
+      <c r="M4" s="63">
         <v>0.22</v>
       </c>
-      <c r="N4" s="67">
+      <c r="N4" s="62">
         <f>J4*M4</f>
         <v>1.32</v>
       </c>
-      <c r="O4" s="112">
+      <c r="O4" s="98">
         <v>0.14699999999999999</v>
       </c>
-      <c r="P4" s="105">
+      <c r="P4" s="92">
         <f t="shared" ref="P4:P43" si="0">O4*K4</f>
         <v>4.41</v>
       </c>
@@ -2318,2381 +2333,2381 @@
       <c r="A5" s="11">
         <v>3</v>
       </c>
-      <c r="B5" s="55"/>
-      <c r="C5" s="128" t="s">
+      <c r="B5" s="137"/>
+      <c r="C5" s="114" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="21" t="s">
+      <c r="D5" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="E5" s="21" t="s">
+      <c r="E5" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="F5" s="62" t="s">
+      <c r="F5" s="57" t="s">
         <v>144</v>
       </c>
-      <c r="G5" s="21" t="s">
+      <c r="G5" s="19" t="s">
         <v>203</v>
       </c>
-      <c r="H5" s="22" t="s">
-        <v>250</v>
-      </c>
-      <c r="I5" s="21" t="s">
+      <c r="H5" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="I5" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="J5" s="23">
+      <c r="J5" s="21">
         <v>2</v>
       </c>
-      <c r="K5" s="24">
+      <c r="K5" s="22">
         <f t="shared" ref="K5:K43" si="1">J5*5</f>
         <v>10</v>
       </c>
-      <c r="L5" s="42" t="s">
+      <c r="L5" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="M5" s="27">
+      <c r="M5" s="25">
         <v>0.52</v>
       </c>
-      <c r="N5" s="67">
+      <c r="N5" s="62">
         <f t="shared" ref="N5:N43" si="2">J5*M5</f>
         <v>1.04</v>
       </c>
-      <c r="O5" s="113">
+      <c r="O5" s="99">
         <v>0.36499999999999999</v>
       </c>
-      <c r="P5" s="105">
+      <c r="P5" s="92">
         <f t="shared" si="0"/>
         <v>3.65</v>
       </c>
       <c r="Q5" s="7"/>
     </row>
     <row r="6" spans="1:17" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="141">
+      <c r="A6" s="127">
         <v>4</v>
       </c>
-      <c r="B6" s="55"/>
-      <c r="C6" s="128" t="s">
+      <c r="B6" s="137"/>
+      <c r="C6" s="114" t="s">
         <v>30</v>
       </c>
-      <c r="D6" s="21" t="s">
+      <c r="D6" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="E6" s="21" t="s">
+      <c r="E6" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="F6" s="62" t="s">
+      <c r="F6" s="57" t="s">
         <v>145</v>
       </c>
-      <c r="G6" s="21" t="s">
+      <c r="G6" s="19" t="s">
         <v>203</v>
       </c>
-      <c r="H6" s="22" t="s">
-        <v>250</v>
-      </c>
-      <c r="I6" s="21" t="s">
+      <c r="H6" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="I6" s="19" t="s">
         <v>178</v>
       </c>
-      <c r="J6" s="23">
+      <c r="J6" s="21">
         <v>11</v>
       </c>
-      <c r="K6" s="24">
+      <c r="K6" s="22">
         <f>J6*5</f>
         <v>55</v>
       </c>
-      <c r="L6" s="42" t="s">
+      <c r="L6" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="M6" s="25">
+      <c r="M6" s="23">
         <v>5.0999999999999997E-2</v>
       </c>
-      <c r="N6" s="67">
+      <c r="N6" s="62">
         <f t="shared" si="2"/>
         <v>0.56099999999999994</v>
       </c>
-      <c r="O6" s="112">
+      <c r="O6" s="98">
         <v>2.7799999999999998E-2</v>
       </c>
-      <c r="P6" s="105">
+      <c r="P6" s="92">
         <f t="shared" si="0"/>
         <v>1.5289999999999999</v>
       </c>
       <c r="Q6" s="7"/>
     </row>
     <row r="7" spans="1:17" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="141">
+      <c r="A7" s="127">
         <v>5</v>
       </c>
-      <c r="B7" s="55"/>
-      <c r="C7" s="128" t="s">
+      <c r="B7" s="137"/>
+      <c r="C7" s="114" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="21" t="s">
+      <c r="D7" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="E7" s="21" t="s">
+      <c r="E7" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="F7" s="62" t="s">
+      <c r="F7" s="57" t="s">
         <v>146</v>
       </c>
-      <c r="G7" s="21" t="s">
+      <c r="G7" s="19" t="s">
         <v>204</v>
       </c>
-      <c r="H7" s="22" t="s">
-        <v>250</v>
-      </c>
-      <c r="I7" s="21" t="s">
+      <c r="H7" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="I7" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="J7" s="23">
+      <c r="J7" s="21">
         <v>10</v>
       </c>
-      <c r="K7" s="24">
+      <c r="K7" s="22">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="L7" s="42" t="s">
+      <c r="L7" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="M7" s="28">
+      <c r="M7" s="26">
         <v>0.189</v>
       </c>
-      <c r="N7" s="67">
+      <c r="N7" s="62">
         <f>J7*M7</f>
         <v>1.8900000000000001</v>
       </c>
-      <c r="O7" s="114">
+      <c r="O7" s="100">
         <v>0.1132</v>
       </c>
-      <c r="P7" s="105">
+      <c r="P7" s="92">
         <f t="shared" si="0"/>
         <v>5.66</v>
       </c>
       <c r="Q7" s="7"/>
     </row>
     <row r="8" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="141">
+      <c r="A8" s="127">
         <v>6</v>
       </c>
-      <c r="B8" s="55"/>
-      <c r="C8" s="128" t="s">
+      <c r="B8" s="137"/>
+      <c r="C8" s="114" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="21" t="s">
+      <c r="D8" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="E8" s="21" t="s">
+      <c r="E8" s="19" t="s">
         <v>117</v>
       </c>
-      <c r="F8" s="62" t="s">
+      <c r="F8" s="57" t="s">
         <v>147</v>
       </c>
-      <c r="G8" s="21" t="s">
+      <c r="G8" s="19" t="s">
         <v>203</v>
       </c>
-      <c r="H8" s="22" t="s">
-        <v>250</v>
-      </c>
-      <c r="I8" s="21" t="s">
+      <c r="H8" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="I8" s="19" t="s">
         <v>180</v>
       </c>
-      <c r="J8" s="23">
+      <c r="J8" s="21">
         <v>1</v>
       </c>
-      <c r="K8" s="24">
+      <c r="K8" s="22">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L8" s="42" t="s">
+      <c r="L8" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="M8" s="25">
+      <c r="M8" s="23">
         <v>0.1</v>
       </c>
-      <c r="N8" s="67">
+      <c r="N8" s="62">
         <f t="shared" si="2"/>
         <v>0.1</v>
       </c>
-      <c r="O8" s="112">
+      <c r="O8" s="98">
         <v>0.1</v>
       </c>
-      <c r="P8" s="105">
+      <c r="P8" s="92">
         <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="Q8" s="7"/>
     </row>
     <row r="9" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="141">
+      <c r="A9" s="127">
         <v>7</v>
       </c>
-      <c r="B9" s="55"/>
-      <c r="C9" s="128" t="s">
+      <c r="B9" s="137"/>
+      <c r="C9" s="114" t="s">
         <v>33</v>
       </c>
-      <c r="D9" s="21" t="s">
+      <c r="D9" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="E9" s="21" t="s">
+      <c r="E9" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="F9" s="62" t="s">
+      <c r="F9" s="57" t="s">
         <v>148</v>
       </c>
-      <c r="G9" s="21" t="s">
+      <c r="G9" s="19" t="s">
         <v>205</v>
       </c>
-      <c r="H9" s="22" t="s">
-        <v>250</v>
-      </c>
-      <c r="I9" s="21" t="s">
+      <c r="H9" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="I9" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="J9" s="23">
+      <c r="J9" s="21">
         <v>1</v>
       </c>
-      <c r="K9" s="24">
+      <c r="K9" s="22">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L9" s="42" t="s">
+      <c r="L9" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="M9" s="25">
+      <c r="M9" s="23">
         <v>0.32</v>
       </c>
-      <c r="N9" s="67">
+      <c r="N9" s="62">
         <f t="shared" si="2"/>
         <v>0.32</v>
       </c>
-      <c r="O9" s="112">
+      <c r="O9" s="98">
         <v>0.32</v>
       </c>
-      <c r="P9" s="105">
+      <c r="P9" s="92">
         <f t="shared" si="0"/>
         <v>1.6</v>
       </c>
       <c r="Q9" s="7"/>
     </row>
     <row r="10" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="141">
+      <c r="A10" s="127">
         <v>8</v>
       </c>
-      <c r="B10" s="55"/>
-      <c r="C10" s="128" t="s">
+      <c r="B10" s="137"/>
+      <c r="C10" s="114" t="s">
         <v>34</v>
       </c>
-      <c r="D10" s="21" t="s">
+      <c r="D10" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="E10" s="21" t="s">
+      <c r="E10" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="F10" s="62" t="s">
+      <c r="F10" s="57" t="s">
         <v>149</v>
       </c>
-      <c r="G10" s="21" t="s">
+      <c r="G10" s="19" t="s">
         <v>203</v>
       </c>
-      <c r="H10" s="22" t="s">
-        <v>250</v>
-      </c>
-      <c r="I10" s="21" t="s">
+      <c r="H10" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="I10" s="19" t="s">
         <v>182</v>
       </c>
-      <c r="J10" s="23">
+      <c r="J10" s="21">
         <v>1</v>
       </c>
-      <c r="K10" s="24">
+      <c r="K10" s="22">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L10" s="42" t="s">
+      <c r="L10" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="M10" s="27">
+      <c r="M10" s="25">
         <v>0.32</v>
       </c>
-      <c r="N10" s="67">
+      <c r="N10" s="62">
         <f t="shared" si="2"/>
         <v>0.32</v>
       </c>
-      <c r="O10" s="113">
+      <c r="O10" s="99">
         <v>0.32</v>
       </c>
-      <c r="P10" s="105">
+      <c r="P10" s="92">
         <f t="shared" si="0"/>
         <v>1.6</v>
       </c>
       <c r="Q10" s="7"/>
     </row>
     <row r="11" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="141">
+      <c r="A11" s="127">
         <v>9</v>
       </c>
-      <c r="B11" s="55"/>
-      <c r="C11" s="128" t="s">
+      <c r="B11" s="137"/>
+      <c r="C11" s="114" t="s">
         <v>35</v>
       </c>
-      <c r="D11" s="21" t="s">
+      <c r="D11" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="E11" s="21" t="s">
+      <c r="E11" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="F11" s="62" t="s">
+      <c r="F11" s="57" t="s">
         <v>150</v>
       </c>
-      <c r="G11" s="21" t="s">
+      <c r="G11" s="19" t="s">
         <v>206</v>
       </c>
-      <c r="H11" s="22" t="s">
-        <v>250</v>
-      </c>
-      <c r="I11" s="21" t="s">
+      <c r="H11" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="I11" s="19" t="s">
         <v>183</v>
       </c>
-      <c r="J11" s="23">
+      <c r="J11" s="21">
         <v>1</v>
       </c>
-      <c r="K11" s="24">
+      <c r="K11" s="22">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L11" s="42" t="s">
+      <c r="L11" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="M11" s="29">
+      <c r="M11" s="27">
         <v>0.1</v>
       </c>
-      <c r="N11" s="67">
+      <c r="N11" s="62">
         <f t="shared" si="2"/>
         <v>0.1</v>
       </c>
-      <c r="O11" s="112">
+      <c r="O11" s="98">
         <v>0.1</v>
       </c>
-      <c r="P11" s="105">
+      <c r="P11" s="92">
         <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="Q11" s="7"/>
     </row>
     <row r="12" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="141">
+      <c r="A12" s="127">
         <v>10</v>
       </c>
-      <c r="B12" s="55"/>
-      <c r="C12" s="128" t="s">
+      <c r="B12" s="137"/>
+      <c r="C12" s="114" t="s">
         <v>36</v>
       </c>
-      <c r="D12" s="21" t="s">
+      <c r="D12" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="E12" s="21" t="s">
+      <c r="E12" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="F12" s="62" t="s">
+      <c r="F12" s="57" t="s">
         <v>151</v>
       </c>
-      <c r="G12" s="21" t="s">
+      <c r="G12" s="19" t="s">
         <v>207</v>
       </c>
-      <c r="H12" s="22" t="s">
-        <v>250</v>
-      </c>
-      <c r="I12" s="21" t="s">
+      <c r="H12" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="I12" s="19" t="s">
         <v>184</v>
       </c>
-      <c r="J12" s="23">
+      <c r="J12" s="21">
         <v>2</v>
       </c>
-      <c r="K12" s="24">
+      <c r="K12" s="22">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="L12" s="42" t="s">
+      <c r="L12" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="M12" s="25">
+      <c r="M12" s="23">
         <v>0.47</v>
       </c>
-      <c r="N12" s="67">
+      <c r="N12" s="62">
         <f t="shared" si="2"/>
         <v>0.94</v>
       </c>
-      <c r="O12" s="112">
+      <c r="O12" s="98">
         <v>0.33100000000000002</v>
       </c>
-      <c r="P12" s="105">
+      <c r="P12" s="92">
         <f t="shared" si="0"/>
         <v>3.31</v>
       </c>
       <c r="Q12" s="7"/>
     </row>
     <row r="13" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="141">
+      <c r="A13" s="127">
         <v>11</v>
       </c>
-      <c r="B13" s="55"/>
-      <c r="C13" s="129" t="s">
+      <c r="B13" s="137"/>
+      <c r="C13" s="115" t="s">
         <v>37</v>
       </c>
-      <c r="D13" s="45" t="s">
+      <c r="D13" s="43" t="s">
         <v>82</v>
       </c>
-      <c r="E13" s="45" t="s">
+      <c r="E13" s="43" t="s">
         <v>115</v>
       </c>
-      <c r="F13" s="87" t="s">
+      <c r="F13" s="74" t="s">
         <v>152</v>
       </c>
-      <c r="G13" s="45" t="s">
+      <c r="G13" s="43" t="s">
         <v>208</v>
       </c>
-      <c r="H13" s="51" t="s">
-        <v>250</v>
-      </c>
-      <c r="I13" s="45" t="s">
+      <c r="H13" s="49" t="s">
+        <v>250</v>
+      </c>
+      <c r="I13" s="43" t="s">
         <v>185</v>
       </c>
-      <c r="J13" s="46">
+      <c r="J13" s="44">
         <v>1</v>
       </c>
-      <c r="K13" s="48">
+      <c r="K13" s="46">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L13" s="49" t="s">
+      <c r="L13" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="M13" s="47">
+      <c r="M13" s="45">
         <v>0.1</v>
       </c>
-      <c r="N13" s="88">
+      <c r="N13" s="75">
         <f t="shared" si="2"/>
         <v>0.1</v>
       </c>
-      <c r="O13" s="115">
+      <c r="O13" s="101">
         <v>0.1</v>
       </c>
-      <c r="P13" s="106">
+      <c r="P13" s="93">
         <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
-      <c r="Q13" s="50"/>
+      <c r="Q13" s="48"/>
     </row>
     <row r="14" spans="1:17" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="141">
+      <c r="A14" s="127">
         <v>12</v>
       </c>
-      <c r="B14" s="72" t="s">
+      <c r="B14" s="64" t="s">
         <v>235</v>
       </c>
-      <c r="C14" s="130" t="s">
+      <c r="C14" s="116" t="s">
         <v>38</v>
       </c>
-      <c r="D14" s="34" t="s">
+      <c r="D14" s="32" t="s">
         <v>83</v>
       </c>
-      <c r="E14" s="34" t="s">
+      <c r="E14" s="32" t="s">
         <v>119</v>
       </c>
-      <c r="F14" s="64" t="s">
+      <c r="F14" s="59" t="s">
         <v>236</v>
       </c>
-      <c r="G14" s="34" t="s">
+      <c r="G14" s="32" t="s">
         <v>209</v>
       </c>
-      <c r="H14" s="89" t="s">
-        <v>250</v>
-      </c>
-      <c r="I14" s="34" t="s">
-        <v>250</v>
-      </c>
-      <c r="J14" s="35">
+      <c r="H14" s="76" t="s">
+        <v>250</v>
+      </c>
+      <c r="I14" s="32" t="s">
+        <v>250</v>
+      </c>
+      <c r="J14" s="33">
         <v>2</v>
       </c>
-      <c r="K14" s="36">
+      <c r="K14" s="34">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="L14" s="44" t="s">
+      <c r="L14" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="M14" s="37">
+      <c r="M14" s="35">
         <v>0.53</v>
       </c>
-      <c r="N14" s="57">
+      <c r="N14" s="52">
         <f t="shared" si="2"/>
         <v>1.06</v>
       </c>
-      <c r="O14" s="116">
+      <c r="O14" s="102">
         <v>0.45400000000000001</v>
       </c>
-      <c r="P14" s="107">
+      <c r="P14" s="94">
         <f t="shared" si="0"/>
         <v>4.54</v>
       </c>
       <c r="Q14" s="10"/>
     </row>
-    <row r="15" spans="1:17" s="53" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="141">
+    <row r="15" spans="1:17" s="51" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="127">
         <v>13</v>
       </c>
-      <c r="B15" s="54" t="s">
+      <c r="B15" s="134" t="s">
         <v>229</v>
       </c>
-      <c r="C15" s="137" t="s">
+      <c r="C15" s="123" t="s">
         <v>43</v>
       </c>
-      <c r="D15" s="60" t="s">
+      <c r="D15" s="55" t="s">
         <v>89</v>
       </c>
-      <c r="E15" s="60" t="s">
+      <c r="E15" s="55" t="s">
         <v>244</v>
       </c>
-      <c r="F15" s="138" t="s">
+      <c r="F15" s="124" t="s">
         <v>125</v>
       </c>
-      <c r="G15" s="60" t="s">
+      <c r="G15" s="55" t="s">
         <v>213</v>
       </c>
-      <c r="H15" s="16" t="s">
-        <v>250</v>
-      </c>
-      <c r="I15" s="60" t="s">
+      <c r="H15" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="I15" s="55" t="s">
         <v>186</v>
       </c>
-      <c r="J15" s="38">
+      <c r="J15" s="36">
         <v>1</v>
       </c>
-      <c r="K15" s="18">
+      <c r="K15" s="16">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L15" s="41" t="s">
+      <c r="L15" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="M15" s="19">
+      <c r="M15" s="17">
         <v>0.55000000000000004</v>
       </c>
-      <c r="N15" s="20">
+      <c r="N15" s="18">
         <f t="shared" si="2"/>
         <v>0.55000000000000004</v>
       </c>
-      <c r="O15" s="117">
+      <c r="O15" s="103">
         <v>0.55000000000000004</v>
       </c>
-      <c r="P15" s="104">
+      <c r="P15" s="91">
         <f t="shared" si="0"/>
         <v>2.75</v>
       </c>
       <c r="Q15" s="6"/>
     </row>
     <row r="16" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="141">
+      <c r="A16" s="127">
         <v>14</v>
       </c>
-      <c r="B16" s="73"/>
-      <c r="C16" s="128" t="s">
+      <c r="B16" s="135"/>
+      <c r="C16" s="114" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="21" t="s">
+      <c r="D16" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="E16" s="21" t="s">
+      <c r="E16" s="19" t="s">
         <v>244</v>
       </c>
-      <c r="F16" s="62" t="s">
+      <c r="F16" s="57" t="s">
         <v>126</v>
       </c>
-      <c r="G16" s="21" t="s">
+      <c r="G16" s="19" t="s">
         <v>213</v>
       </c>
-      <c r="H16" s="22" t="s">
-        <v>250</v>
-      </c>
-      <c r="I16" s="21" t="s">
+      <c r="H16" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="I16" s="19" t="s">
         <v>187</v>
       </c>
-      <c r="J16" s="23">
+      <c r="J16" s="21">
         <v>1</v>
       </c>
-      <c r="K16" s="24">
+      <c r="K16" s="22">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L16" s="42" t="s">
+      <c r="L16" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="M16" s="25">
+      <c r="M16" s="23">
         <v>0.92</v>
       </c>
-      <c r="N16" s="67">
+      <c r="N16" s="62">
         <f t="shared" si="2"/>
         <v>0.92</v>
       </c>
-      <c r="O16" s="112">
+      <c r="O16" s="98">
         <v>0.92</v>
       </c>
-      <c r="P16" s="105">
+      <c r="P16" s="92">
         <f t="shared" si="0"/>
         <v>4.6000000000000005</v>
       </c>
       <c r="Q16" s="8"/>
     </row>
     <row r="17" spans="1:17" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="141">
+      <c r="A17" s="127">
         <v>5</v>
       </c>
-      <c r="B17" s="74"/>
-      <c r="C17" s="131" t="s">
+      <c r="B17" s="136"/>
+      <c r="C17" s="117" t="s">
         <v>45</v>
       </c>
-      <c r="D17" s="30" t="s">
+      <c r="D17" s="28" t="s">
         <v>91</v>
       </c>
-      <c r="E17" s="30" t="s">
+      <c r="E17" s="28" t="s">
         <v>127</v>
       </c>
-      <c r="F17" s="63" t="s">
+      <c r="F17" s="58" t="s">
         <v>153</v>
       </c>
-      <c r="G17" s="30" t="s">
+      <c r="G17" s="28" t="s">
         <v>205</v>
       </c>
-      <c r="H17" s="58" t="s">
-        <v>250</v>
-      </c>
-      <c r="I17" s="30" t="s">
+      <c r="H17" s="53" t="s">
+        <v>250</v>
+      </c>
+      <c r="I17" s="28" t="s">
         <v>188</v>
       </c>
-      <c r="J17" s="31">
+      <c r="J17" s="29">
         <v>1</v>
       </c>
-      <c r="K17" s="32">
+      <c r="K17" s="30">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L17" s="43" t="s">
+      <c r="L17" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="M17" s="33">
+      <c r="M17" s="31">
         <v>0.38</v>
       </c>
-      <c r="N17" s="86">
+      <c r="N17" s="73">
         <f t="shared" si="2"/>
         <v>0.38</v>
       </c>
-      <c r="O17" s="118">
+      <c r="O17" s="104">
         <v>0.38</v>
       </c>
-      <c r="P17" s="108">
+      <c r="P17" s="95">
         <f t="shared" si="0"/>
         <v>1.9</v>
       </c>
       <c r="Q17" s="9"/>
     </row>
     <row r="18" spans="1:17" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="141">
+      <c r="A18" s="127">
         <v>16</v>
       </c>
-      <c r="B18" s="72" t="s">
+      <c r="B18" s="64" t="s">
         <v>20</v>
       </c>
-      <c r="C18" s="130" t="s">
+      <c r="C18" s="116" t="s">
         <v>46</v>
       </c>
-      <c r="D18" s="34" t="s">
+      <c r="D18" s="32" t="s">
         <v>92</v>
       </c>
-      <c r="E18" s="34" t="s">
+      <c r="E18" s="32" t="s">
         <v>128</v>
       </c>
-      <c r="F18" s="64" t="s">
+      <c r="F18" s="59" t="s">
         <v>154</v>
       </c>
-      <c r="G18" s="34" t="s">
+      <c r="G18" s="32" t="s">
         <v>214</v>
       </c>
-      <c r="H18" s="59" t="s">
-        <v>250</v>
-      </c>
-      <c r="I18" s="34" t="s">
+      <c r="H18" s="54" t="s">
+        <v>250</v>
+      </c>
+      <c r="I18" s="32" t="s">
         <v>254</v>
       </c>
-      <c r="J18" s="35">
+      <c r="J18" s="33">
         <v>1</v>
       </c>
-      <c r="K18" s="36">
+      <c r="K18" s="34">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L18" s="44" t="s">
+      <c r="L18" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="M18" s="37">
+      <c r="M18" s="35">
         <v>0.34</v>
       </c>
-      <c r="N18" s="57">
+      <c r="N18" s="52">
         <f t="shared" si="2"/>
         <v>0.34</v>
       </c>
-      <c r="O18" s="116">
+      <c r="O18" s="102">
         <v>0.34</v>
       </c>
-      <c r="P18" s="107">
+      <c r="P18" s="94">
         <f t="shared" si="0"/>
         <v>1.7000000000000002</v>
       </c>
       <c r="Q18" s="10"/>
     </row>
     <row r="19" spans="1:17" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="141">
+      <c r="A19" s="127">
         <v>17</v>
       </c>
-      <c r="B19" s="72" t="s">
+      <c r="B19" s="64" t="s">
         <v>230</v>
       </c>
-      <c r="C19" s="130" t="s">
+      <c r="C19" s="116" t="s">
         <v>47</v>
       </c>
-      <c r="D19" s="34" t="s">
+      <c r="D19" s="32" t="s">
         <v>93</v>
       </c>
-      <c r="E19" s="34" t="s">
+      <c r="E19" s="32" t="s">
         <v>129</v>
       </c>
-      <c r="F19" s="64" t="s">
+      <c r="F19" s="59" t="s">
         <v>155</v>
       </c>
-      <c r="G19" s="34" t="s">
+      <c r="G19" s="32" t="s">
         <v>215</v>
       </c>
-      <c r="H19" s="59" t="s">
-        <v>250</v>
-      </c>
-      <c r="I19" s="34" t="s">
+      <c r="H19" s="54" t="s">
+        <v>250</v>
+      </c>
+      <c r="I19" s="32" t="s">
         <v>254</v>
       </c>
-      <c r="J19" s="35">
+      <c r="J19" s="33">
         <v>1</v>
       </c>
-      <c r="K19" s="36">
+      <c r="K19" s="34">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L19" s="44" t="s">
+      <c r="L19" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="M19" s="37">
+      <c r="M19" s="35">
         <v>0.41</v>
       </c>
-      <c r="N19" s="57">
+      <c r="N19" s="52">
         <f t="shared" si="2"/>
         <v>0.41</v>
       </c>
-      <c r="O19" s="116">
+      <c r="O19" s="102">
         <v>0.41</v>
       </c>
-      <c r="P19" s="107">
+      <c r="P19" s="94">
         <f t="shared" si="0"/>
         <v>2.0499999999999998</v>
       </c>
       <c r="Q19" s="10"/>
     </row>
     <row r="20" spans="1:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="141">
+      <c r="A20" s="127">
         <v>18</v>
       </c>
-      <c r="B20" s="54" t="s">
+      <c r="B20" s="134" t="s">
         <v>231</v>
       </c>
-      <c r="C20" s="126" t="s">
+      <c r="C20" s="112" t="s">
         <v>48</v>
       </c>
-      <c r="D20" s="15" t="s">
+      <c r="D20" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="E20" s="15" t="s">
+      <c r="E20" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="F20" s="61" t="s">
+      <c r="F20" s="56" t="s">
         <v>156</v>
       </c>
-      <c r="G20" s="15" t="s">
+      <c r="G20" s="13" t="s">
         <v>216</v>
       </c>
-      <c r="H20" s="60" t="s">
-        <v>250</v>
-      </c>
-      <c r="I20" s="15" t="s">
+      <c r="H20" s="55" t="s">
+        <v>250</v>
+      </c>
+      <c r="I20" s="13" t="s">
         <v>189</v>
       </c>
-      <c r="J20" s="17">
+      <c r="J20" s="15">
         <v>2</v>
       </c>
-      <c r="K20" s="18">
+      <c r="K20" s="16">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="L20" s="41" t="s">
+      <c r="L20" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="M20" s="39">
+      <c r="M20" s="37">
         <v>0.1</v>
       </c>
-      <c r="N20" s="20">
+      <c r="N20" s="18">
         <f t="shared" si="2"/>
         <v>0.2</v>
       </c>
-      <c r="O20" s="119">
+      <c r="O20" s="105">
         <v>2.5999999999999999E-2</v>
       </c>
-      <c r="P20" s="104">
+      <c r="P20" s="91">
         <f t="shared" si="0"/>
         <v>0.26</v>
       </c>
       <c r="Q20" s="6"/>
     </row>
     <row r="21" spans="1:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="141">
+      <c r="A21" s="127">
         <v>19</v>
       </c>
-      <c r="B21" s="55"/>
-      <c r="C21" s="128" t="s">
+      <c r="B21" s="137"/>
+      <c r="C21" s="114" t="s">
         <v>49</v>
       </c>
-      <c r="D21" s="21" t="s">
+      <c r="D21" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="E21" s="21" t="s">
+      <c r="E21" s="19" t="s">
         <v>130</v>
       </c>
-      <c r="F21" s="62" t="s">
+      <c r="F21" s="57" t="s">
         <v>157</v>
       </c>
-      <c r="G21" s="21" t="s">
+      <c r="G21" s="19" t="s">
         <v>206</v>
       </c>
-      <c r="H21" s="52" t="s">
-        <v>250</v>
-      </c>
-      <c r="I21" s="21" t="s">
+      <c r="H21" s="50" t="s">
+        <v>250</v>
+      </c>
+      <c r="I21" s="19" t="s">
         <v>190</v>
       </c>
-      <c r="J21" s="23">
+      <c r="J21" s="21">
         <v>1</v>
       </c>
-      <c r="K21" s="24">
+      <c r="K21" s="22">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L21" s="42" t="s">
+      <c r="L21" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="M21" s="25">
+      <c r="M21" s="23">
         <v>0.1</v>
       </c>
-      <c r="N21" s="67">
+      <c r="N21" s="62">
         <f t="shared" si="2"/>
         <v>0.1</v>
       </c>
-      <c r="O21" s="112">
+      <c r="O21" s="98">
         <v>0.1</v>
       </c>
-      <c r="P21" s="105">
+      <c r="P21" s="92">
         <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="Q21" s="8"/>
     </row>
     <row r="22" spans="1:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="141">
+      <c r="A22" s="127">
         <v>20</v>
       </c>
-      <c r="B22" s="55"/>
-      <c r="C22" s="128" t="s">
+      <c r="B22" s="137"/>
+      <c r="C22" s="114" t="s">
         <v>50</v>
       </c>
-      <c r="D22" s="21" t="s">
+      <c r="D22" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="E22" s="21" t="s">
+      <c r="E22" s="19" t="s">
         <v>130</v>
       </c>
-      <c r="F22" s="62" t="s">
+      <c r="F22" s="57" t="s">
         <v>158</v>
       </c>
-      <c r="G22" s="21" t="s">
+      <c r="G22" s="19" t="s">
         <v>206</v>
       </c>
-      <c r="H22" s="52" t="s">
-        <v>250</v>
-      </c>
-      <c r="I22" s="21" t="s">
+      <c r="H22" s="50" t="s">
+        <v>250</v>
+      </c>
+      <c r="I22" s="19" t="s">
         <v>191</v>
       </c>
-      <c r="J22" s="23">
+      <c r="J22" s="21">
         <v>1</v>
       </c>
-      <c r="K22" s="24">
+      <c r="K22" s="22">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L22" s="42" t="s">
+      <c r="L22" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="M22" s="25">
+      <c r="M22" s="23">
         <v>0.1</v>
       </c>
-      <c r="N22" s="67">
+      <c r="N22" s="62">
         <f t="shared" si="2"/>
         <v>0.1</v>
       </c>
-      <c r="O22" s="112">
+      <c r="O22" s="98">
         <v>0.1</v>
       </c>
-      <c r="P22" s="105">
+      <c r="P22" s="92">
         <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="Q22" s="8"/>
     </row>
     <row r="23" spans="1:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="141">
+      <c r="A23" s="127">
         <v>21</v>
       </c>
-      <c r="B23" s="55"/>
-      <c r="C23" s="128" t="s">
+      <c r="B23" s="137"/>
+      <c r="C23" s="114" t="s">
         <v>51</v>
       </c>
-      <c r="D23" s="21" t="s">
+      <c r="D23" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="E23" s="21" t="s">
+      <c r="E23" s="19" t="s">
         <v>130</v>
       </c>
-      <c r="F23" s="62" t="s">
+      <c r="F23" s="57" t="s">
         <v>159</v>
       </c>
-      <c r="G23" s="21" t="s">
+      <c r="G23" s="19" t="s">
         <v>206</v>
       </c>
-      <c r="H23" s="52" t="s">
-        <v>250</v>
-      </c>
-      <c r="I23" s="21" t="s">
+      <c r="H23" s="50" t="s">
+        <v>250</v>
+      </c>
+      <c r="I23" s="19" t="s">
         <v>192</v>
       </c>
-      <c r="J23" s="23">
+      <c r="J23" s="21">
         <v>1</v>
       </c>
-      <c r="K23" s="24">
+      <c r="K23" s="22">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L23" s="42" t="s">
+      <c r="L23" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="M23" s="25">
+      <c r="M23" s="23">
         <v>0.1</v>
       </c>
-      <c r="N23" s="67">
+      <c r="N23" s="62">
         <f t="shared" si="2"/>
         <v>0.1</v>
       </c>
-      <c r="O23" s="112">
+      <c r="O23" s="98">
         <v>0.1</v>
       </c>
-      <c r="P23" s="105">
+      <c r="P23" s="92">
         <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="Q23" s="8"/>
     </row>
     <row r="24" spans="1:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="141">
+      <c r="A24" s="127">
         <v>22</v>
       </c>
-      <c r="B24" s="55"/>
-      <c r="C24" s="128" t="s">
+      <c r="B24" s="137"/>
+      <c r="C24" s="114" t="s">
         <v>52</v>
       </c>
-      <c r="D24" s="21" t="s">
+      <c r="D24" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="E24" s="21" t="s">
+      <c r="E24" s="19" t="s">
         <v>130</v>
       </c>
-      <c r="F24" s="62" t="s">
+      <c r="F24" s="57" t="s">
         <v>160</v>
       </c>
-      <c r="G24" s="21" t="s">
+      <c r="G24" s="19" t="s">
         <v>206</v>
       </c>
-      <c r="H24" s="52" t="s">
-        <v>250</v>
-      </c>
-      <c r="I24" s="21" t="s">
+      <c r="H24" s="50" t="s">
+        <v>250</v>
+      </c>
+      <c r="I24" s="19" t="s">
         <v>193</v>
       </c>
-      <c r="J24" s="23">
+      <c r="J24" s="21">
         <v>1</v>
       </c>
-      <c r="K24" s="24">
+      <c r="K24" s="22">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L24" s="42" t="s">
+      <c r="L24" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="M24" s="25">
+      <c r="M24" s="23">
         <v>0.1</v>
       </c>
-      <c r="N24" s="67">
+      <c r="N24" s="62">
         <f t="shared" si="2"/>
         <v>0.1</v>
       </c>
-      <c r="O24" s="112">
+      <c r="O24" s="98">
         <v>0.1</v>
       </c>
-      <c r="P24" s="105">
+      <c r="P24" s="92">
         <f>O24*K24</f>
         <v>0.5</v>
       </c>
       <c r="Q24" s="8"/>
     </row>
     <row r="25" spans="1:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="141">
+      <c r="A25" s="127">
         <v>23</v>
       </c>
-      <c r="B25" s="55"/>
-      <c r="C25" s="128" t="s">
+      <c r="B25" s="137"/>
+      <c r="C25" s="114" t="s">
         <v>54</v>
       </c>
-      <c r="D25" s="21" t="s">
+      <c r="D25" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="E25" s="21" t="s">
+      <c r="E25" s="19" t="s">
         <v>131</v>
       </c>
-      <c r="F25" s="62" t="s">
+      <c r="F25" s="57" t="s">
         <v>162</v>
       </c>
-      <c r="G25" s="21" t="s">
+      <c r="G25" s="19" t="s">
         <v>217</v>
       </c>
-      <c r="H25" s="52" t="s">
-        <v>250</v>
-      </c>
-      <c r="I25" s="21" t="s">
+      <c r="H25" s="50" t="s">
+        <v>250</v>
+      </c>
+      <c r="I25" s="19" t="s">
         <v>245</v>
       </c>
-      <c r="J25" s="23">
+      <c r="J25" s="21">
         <v>2</v>
       </c>
-      <c r="K25" s="24">
+      <c r="K25" s="22">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="L25" s="42" t="s">
+      <c r="L25" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="M25" s="25">
+      <c r="M25" s="23">
         <v>0.12</v>
       </c>
-      <c r="N25" s="67">
+      <c r="N25" s="62">
         <f t="shared" si="2"/>
         <v>0.24</v>
       </c>
-      <c r="O25" s="112">
+      <c r="O25" s="98">
         <v>0.10199999999999999</v>
       </c>
-      <c r="P25" s="105">
+      <c r="P25" s="92">
         <f t="shared" si="0"/>
         <v>1.02</v>
       </c>
       <c r="Q25" s="8"/>
     </row>
     <row r="26" spans="1:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="141">
+      <c r="A26" s="127">
         <v>24</v>
       </c>
-      <c r="B26" s="55"/>
-      <c r="C26" s="128" t="s">
+      <c r="B26" s="137"/>
+      <c r="C26" s="114" t="s">
         <v>55</v>
       </c>
-      <c r="D26" s="21" t="s">
+      <c r="D26" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="E26" s="21" t="s">
+      <c r="E26" s="19" t="s">
         <v>130</v>
       </c>
-      <c r="F26" s="62" t="s">
+      <c r="F26" s="57" t="s">
         <v>163</v>
       </c>
-      <c r="G26" s="21" t="s">
+      <c r="G26" s="19" t="s">
         <v>206</v>
       </c>
-      <c r="H26" s="52" t="s">
-        <v>250</v>
-      </c>
-      <c r="I26" s="21" t="s">
+      <c r="H26" s="50" t="s">
+        <v>250</v>
+      </c>
+      <c r="I26" s="19" t="s">
         <v>194</v>
       </c>
-      <c r="J26" s="23">
+      <c r="J26" s="21">
         <v>2</v>
       </c>
-      <c r="K26" s="24">
+      <c r="K26" s="22">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="L26" s="42" t="s">
+      <c r="L26" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="M26" s="25">
+      <c r="M26" s="23">
         <v>0.1</v>
       </c>
-      <c r="N26" s="67">
+      <c r="N26" s="62">
         <f t="shared" si="2"/>
         <v>0.2</v>
       </c>
-      <c r="O26" s="112">
+      <c r="O26" s="98">
         <v>0.04</v>
       </c>
-      <c r="P26" s="105">
+      <c r="P26" s="92">
         <f t="shared" si="0"/>
         <v>0.4</v>
       </c>
       <c r="Q26" s="8"/>
     </row>
     <row r="27" spans="1:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="141">
+      <c r="A27" s="127">
         <v>25</v>
       </c>
-      <c r="B27" s="55"/>
-      <c r="C27" s="128" t="s">
+      <c r="B27" s="137"/>
+      <c r="C27" s="114" t="s">
         <v>56</v>
       </c>
-      <c r="D27" s="21" t="s">
+      <c r="D27" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="E27" s="21" t="s">
+      <c r="E27" s="19" t="s">
         <v>130</v>
       </c>
-      <c r="F27" s="62" t="s">
+      <c r="F27" s="57" t="s">
         <v>164</v>
       </c>
-      <c r="G27" s="21" t="s">
+      <c r="G27" s="19" t="s">
         <v>206</v>
       </c>
-      <c r="H27" s="52" t="s">
-        <v>250</v>
-      </c>
-      <c r="I27" s="21" t="s">
+      <c r="H27" s="50" t="s">
+        <v>250</v>
+      </c>
+      <c r="I27" s="19" t="s">
         <v>195</v>
       </c>
-      <c r="J27" s="23">
+      <c r="J27" s="21">
         <v>1</v>
       </c>
-      <c r="K27" s="24">
+      <c r="K27" s="22">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L27" s="42" t="s">
+      <c r="L27" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="M27" s="25">
+      <c r="M27" s="23">
         <v>0.1</v>
       </c>
-      <c r="N27" s="67">
+      <c r="N27" s="62">
         <f t="shared" si="2"/>
         <v>0.1</v>
       </c>
-      <c r="O27" s="112">
+      <c r="O27" s="98">
         <v>0.1</v>
       </c>
-      <c r="P27" s="105">
+      <c r="P27" s="92">
         <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="Q27" s="8"/>
     </row>
     <row r="28" spans="1:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="141">
+      <c r="A28" s="127">
         <v>26</v>
       </c>
-      <c r="B28" s="55"/>
-      <c r="C28" s="128" t="s">
+      <c r="B28" s="137"/>
+      <c r="C28" s="114" t="s">
         <v>57</v>
       </c>
-      <c r="D28" s="21" t="s">
+      <c r="D28" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="E28" s="21" t="s">
+      <c r="E28" s="19" t="s">
         <v>130</v>
       </c>
-      <c r="F28" s="62" t="s">
+      <c r="F28" s="57" t="s">
         <v>165</v>
       </c>
-      <c r="G28" s="21" t="s">
+      <c r="G28" s="19" t="s">
         <v>206</v>
       </c>
-      <c r="H28" s="52" t="s">
-        <v>250</v>
-      </c>
-      <c r="I28" s="21" t="s">
+      <c r="H28" s="50" t="s">
+        <v>250</v>
+      </c>
+      <c r="I28" s="19" t="s">
         <v>196</v>
       </c>
-      <c r="J28" s="23">
+      <c r="J28" s="21">
         <v>3</v>
       </c>
-      <c r="K28" s="24">
+      <c r="K28" s="22">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="L28" s="42" t="s">
+      <c r="L28" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="M28" s="25">
+      <c r="M28" s="23">
         <v>0.13</v>
       </c>
-      <c r="N28" s="67">
+      <c r="N28" s="62">
         <f t="shared" si="2"/>
         <v>0.39</v>
       </c>
-      <c r="O28" s="112">
+      <c r="O28" s="98">
         <v>0.113</v>
       </c>
-      <c r="P28" s="105">
+      <c r="P28" s="92">
         <f t="shared" si="0"/>
         <v>1.6950000000000001</v>
       </c>
       <c r="Q28" s="8"/>
     </row>
     <row r="29" spans="1:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="141">
+      <c r="A29" s="127">
         <v>27</v>
       </c>
-      <c r="B29" s="55"/>
-      <c r="C29" s="128" t="s">
+      <c r="B29" s="137"/>
+      <c r="C29" s="114" t="s">
         <v>58</v>
       </c>
-      <c r="D29" s="21" t="s">
+      <c r="D29" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="E29" s="21" t="s">
+      <c r="E29" s="19" t="s">
         <v>131</v>
       </c>
-      <c r="F29" s="65" t="s">
+      <c r="F29" s="60" t="s">
         <v>166</v>
       </c>
-      <c r="G29" s="65" t="s">
+      <c r="G29" s="60" t="s">
         <v>218</v>
       </c>
-      <c r="H29" s="65" t="s">
+      <c r="H29" s="60" t="s">
         <v>237</v>
       </c>
-      <c r="I29" s="65" t="s">
+      <c r="I29" s="60" t="s">
         <v>197</v>
       </c>
-      <c r="J29" s="66">
+      <c r="J29" s="61">
         <v>1</v>
       </c>
-      <c r="K29" s="24">
+      <c r="K29" s="22">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="L29" s="12" t="s">
         <v>252</v>
       </c>
-      <c r="M29" s="25">
+      <c r="M29" s="23">
         <v>0.1</v>
       </c>
-      <c r="N29" s="67">
+      <c r="N29" s="62">
         <f t="shared" si="2"/>
         <v>0.1</v>
       </c>
-      <c r="O29" s="112">
+      <c r="O29" s="98">
         <v>0.1</v>
       </c>
-      <c r="P29" s="105">
+      <c r="P29" s="92">
         <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
-      <c r="Q29" s="121" t="s">
+      <c r="Q29" s="107" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="30" spans="1:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="141">
+      <c r="A30" s="127">
         <v>28</v>
       </c>
-      <c r="B30" s="55"/>
-      <c r="C30" s="128" t="s">
+      <c r="B30" s="137"/>
+      <c r="C30" s="114" t="s">
         <v>53</v>
       </c>
-      <c r="D30" s="21" t="s">
+      <c r="D30" s="19" t="s">
         <v>251</v>
       </c>
-      <c r="E30" s="21" t="s">
+      <c r="E30" s="19" t="s">
         <v>130</v>
       </c>
-      <c r="F30" s="21" t="s">
+      <c r="F30" s="19" t="s">
         <v>161</v>
       </c>
-      <c r="G30" s="21" t="s">
+      <c r="G30" s="19" t="s">
         <v>206</v>
       </c>
-      <c r="H30" s="21" t="s">
-        <v>250</v>
-      </c>
-      <c r="I30" s="21" t="s">
+      <c r="H30" s="19" t="s">
+        <v>250</v>
+      </c>
+      <c r="I30" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="J30" s="23">
+      <c r="J30" s="21">
         <v>5</v>
       </c>
-      <c r="K30" s="24">
+      <c r="K30" s="22">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="L30" s="42" t="s">
+      <c r="L30" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="M30" s="25">
+      <c r="M30" s="23">
         <v>0.1</v>
       </c>
-      <c r="N30" s="67">
+      <c r="N30" s="62">
         <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
-      <c r="O30" s="112">
+      <c r="O30" s="98">
         <v>2.8000000000000001E-2</v>
       </c>
-      <c r="P30" s="105">
+      <c r="P30" s="92">
         <f t="shared" si="0"/>
         <v>0.70000000000000007</v>
       </c>
       <c r="Q30" s="8"/>
     </row>
     <row r="31" spans="1:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="141">
+      <c r="A31" s="127">
         <v>29</v>
       </c>
-      <c r="B31" s="55"/>
-      <c r="C31" s="128" t="s">
+      <c r="B31" s="137"/>
+      <c r="C31" s="114" t="s">
         <v>59</v>
       </c>
-      <c r="D31" s="21" t="s">
+      <c r="D31" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="E31" s="21" t="s">
+      <c r="E31" s="19" t="s">
         <v>130</v>
       </c>
-      <c r="F31" s="62" t="s">
+      <c r="F31" s="57" t="s">
         <v>167</v>
       </c>
-      <c r="G31" s="21" t="s">
+      <c r="G31" s="19" t="s">
         <v>206</v>
       </c>
-      <c r="H31" s="52" t="s">
-        <v>250</v>
-      </c>
-      <c r="I31" s="21" t="s">
+      <c r="H31" s="50" t="s">
+        <v>250</v>
+      </c>
+      <c r="I31" s="19" t="s">
         <v>198</v>
       </c>
-      <c r="J31" s="23">
+      <c r="J31" s="21">
         <v>1</v>
       </c>
-      <c r="K31" s="24">
+      <c r="K31" s="22">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L31" s="42" t="s">
+      <c r="L31" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="M31" s="25">
+      <c r="M31" s="23">
         <v>0.1</v>
       </c>
-      <c r="N31" s="67">
+      <c r="N31" s="62">
         <f t="shared" si="2"/>
         <v>0.1</v>
       </c>
-      <c r="O31" s="112">
+      <c r="O31" s="98">
         <v>0.1</v>
       </c>
-      <c r="P31" s="105">
+      <c r="P31" s="92">
         <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="Q31" s="8"/>
     </row>
     <row r="32" spans="1:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="141">
+      <c r="A32" s="127">
         <v>30</v>
       </c>
-      <c r="B32" s="55"/>
-      <c r="C32" s="128" t="s">
+      <c r="B32" s="137"/>
+      <c r="C32" s="114" t="s">
         <v>60</v>
       </c>
-      <c r="D32" s="21" t="s">
+      <c r="D32" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="E32" s="21" t="s">
+      <c r="E32" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="F32" s="62" t="s">
+      <c r="F32" s="57" t="s">
         <v>168</v>
       </c>
-      <c r="G32" s="21" t="s">
+      <c r="G32" s="19" t="s">
         <v>205</v>
       </c>
-      <c r="H32" s="40" t="s">
+      <c r="H32" s="38" t="s">
         <v>240</v>
       </c>
-      <c r="I32" s="21" t="s">
+      <c r="I32" s="19" t="s">
         <v>199</v>
       </c>
-      <c r="J32" s="23">
+      <c r="J32" s="21">
         <v>1</v>
       </c>
-      <c r="K32" s="24">
+      <c r="K32" s="22">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L32" s="42" t="s">
+      <c r="L32" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="M32" s="25">
+      <c r="M32" s="23">
         <v>0.20100000000000001</v>
       </c>
-      <c r="N32" s="67">
+      <c r="N32" s="62">
         <f t="shared" si="2"/>
         <v>0.20100000000000001</v>
       </c>
-      <c r="O32" s="112">
+      <c r="O32" s="98">
         <v>0.20100000000000001</v>
       </c>
-      <c r="P32" s="105">
+      <c r="P32" s="92">
         <f t="shared" si="0"/>
         <v>1.0050000000000001</v>
       </c>
       <c r="Q32" s="8"/>
     </row>
     <row r="33" spans="1:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="141">
+      <c r="A33" s="127">
         <v>31</v>
       </c>
-      <c r="B33" s="55"/>
-      <c r="C33" s="128" t="s">
+      <c r="B33" s="137"/>
+      <c r="C33" s="114" t="s">
         <v>61</v>
       </c>
-      <c r="D33" s="21" t="s">
+      <c r="D33" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="E33" s="21" t="s">
+      <c r="E33" s="19" t="s">
         <v>130</v>
       </c>
-      <c r="F33" s="62" t="s">
+      <c r="F33" s="57" t="s">
         <v>169</v>
       </c>
-      <c r="G33" s="21" t="s">
+      <c r="G33" s="19" t="s">
         <v>216</v>
       </c>
-      <c r="H33" s="52" t="s">
-        <v>250</v>
-      </c>
-      <c r="I33" s="21" t="s">
+      <c r="H33" s="50" t="s">
+        <v>250</v>
+      </c>
+      <c r="I33" s="19" t="s">
         <v>200</v>
       </c>
-      <c r="J33" s="23">
+      <c r="J33" s="21">
         <v>1</v>
       </c>
-      <c r="K33" s="24">
+      <c r="K33" s="22">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L33" s="42" t="s">
+      <c r="L33" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="M33" s="25">
+      <c r="M33" s="23">
         <v>0.1</v>
       </c>
-      <c r="N33" s="67">
+      <c r="N33" s="62">
         <f t="shared" si="2"/>
         <v>0.1</v>
       </c>
-      <c r="O33" s="112">
+      <c r="O33" s="98">
         <v>0.1</v>
       </c>
-      <c r="P33" s="105">
+      <c r="P33" s="92">
         <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="Q33" s="8"/>
     </row>
     <row r="34" spans="1:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="141">
+      <c r="A34" s="127">
         <v>32</v>
       </c>
-      <c r="B34" s="56"/>
-      <c r="C34" s="131" t="s">
+      <c r="B34" s="138"/>
+      <c r="C34" s="117" t="s">
         <v>62</v>
       </c>
-      <c r="D34" s="30" t="s">
+      <c r="D34" s="28" t="s">
         <v>105</v>
       </c>
-      <c r="E34" s="30" t="s">
+      <c r="E34" s="28" t="s">
         <v>130</v>
       </c>
-      <c r="F34" s="63" t="s">
+      <c r="F34" s="58" t="s">
         <v>170</v>
       </c>
-      <c r="G34" s="30" t="s">
+      <c r="G34" s="28" t="s">
         <v>216</v>
       </c>
-      <c r="H34" s="58" t="s">
-        <v>250</v>
-      </c>
-      <c r="I34" s="30" t="s">
+      <c r="H34" s="53" t="s">
+        <v>250</v>
+      </c>
+      <c r="I34" s="28" t="s">
         <v>201</v>
       </c>
-      <c r="J34" s="31">
+      <c r="J34" s="29">
         <v>1</v>
       </c>
-      <c r="K34" s="32">
+      <c r="K34" s="30">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L34" s="43" t="s">
+      <c r="L34" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="M34" s="33">
+      <c r="M34" s="31">
         <v>0.1</v>
       </c>
-      <c r="N34" s="86">
+      <c r="N34" s="73">
         <f t="shared" si="2"/>
         <v>0.1</v>
       </c>
-      <c r="O34" s="118">
+      <c r="O34" s="104">
         <v>0.1</v>
       </c>
-      <c r="P34" s="108">
+      <c r="P34" s="95">
         <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="Q34" s="9"/>
     </row>
     <row r="35" spans="1:17" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="141">
+      <c r="A35" s="127">
         <v>33</v>
       </c>
-      <c r="B35" s="90" t="s">
+      <c r="B35" s="77" t="s">
         <v>232</v>
       </c>
-      <c r="C35" s="132" t="s">
+      <c r="C35" s="118" t="s">
         <v>64</v>
       </c>
-      <c r="D35" s="91" t="s">
+      <c r="D35" s="78" t="s">
         <v>107</v>
       </c>
-      <c r="E35" s="91" t="s">
+      <c r="E35" s="78" t="s">
         <v>244</v>
       </c>
-      <c r="F35" s="92" t="s">
+      <c r="F35" s="79" t="s">
         <v>134</v>
       </c>
-      <c r="G35" s="91" t="s">
+      <c r="G35" s="78" t="s">
         <v>208</v>
       </c>
-      <c r="H35" s="93" t="s">
-        <v>250</v>
-      </c>
-      <c r="I35" s="91" t="s">
+      <c r="H35" s="80" t="s">
+        <v>250</v>
+      </c>
+      <c r="I35" s="78" t="s">
         <v>245</v>
       </c>
-      <c r="J35" s="94">
+      <c r="J35" s="81">
         <v>1</v>
       </c>
-      <c r="K35" s="95">
+      <c r="K35" s="82">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L35" s="96" t="s">
+      <c r="L35" s="83" t="s">
         <v>14</v>
       </c>
-      <c r="M35" s="97">
+      <c r="M35" s="84">
         <v>0.55000000000000004</v>
       </c>
-      <c r="N35" s="98">
+      <c r="N35" s="85">
         <f t="shared" si="2"/>
         <v>0.55000000000000004</v>
       </c>
-      <c r="O35" s="120">
+      <c r="O35" s="106">
         <v>0.55000000000000004</v>
       </c>
-      <c r="P35" s="109">
+      <c r="P35" s="96">
         <f t="shared" si="0"/>
         <v>2.75</v>
       </c>
-      <c r="Q35" s="125"/>
+      <c r="Q35" s="111"/>
     </row>
     <row r="36" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="141">
+      <c r="A36" s="127">
         <v>34</v>
       </c>
-      <c r="B36" s="54" t="s">
+      <c r="B36" s="134" t="s">
         <v>233</v>
       </c>
-      <c r="C36" s="126" t="s">
+      <c r="C36" s="112" t="s">
         <v>65</v>
       </c>
-      <c r="D36" s="15" t="s">
+      <c r="D36" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="E36" s="15" t="s">
+      <c r="E36" s="13" t="s">
         <v>248</v>
       </c>
-      <c r="F36" s="61" t="s">
+      <c r="F36" s="56" t="s">
         <v>135</v>
       </c>
-      <c r="G36" s="15" t="s">
+      <c r="G36" s="13" t="s">
         <v>219</v>
       </c>
-      <c r="H36" s="60" t="s">
-        <v>250</v>
-      </c>
-      <c r="I36" s="15" t="s">
+      <c r="H36" s="55" t="s">
+        <v>250</v>
+      </c>
+      <c r="I36" s="13" t="s">
         <v>245</v>
       </c>
-      <c r="J36" s="17">
+      <c r="J36" s="15">
         <v>1</v>
       </c>
-      <c r="K36" s="18">
+      <c r="K36" s="16">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L36" s="41" t="s">
+      <c r="L36" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="M36" s="39">
+      <c r="M36" s="37">
         <v>3.13</v>
       </c>
-      <c r="N36" s="20">
+      <c r="N36" s="18">
         <f t="shared" si="2"/>
         <v>3.13</v>
       </c>
-      <c r="O36" s="119">
+      <c r="O36" s="105">
         <v>3.13</v>
       </c>
-      <c r="P36" s="104">
+      <c r="P36" s="91">
         <f t="shared" si="0"/>
         <v>15.649999999999999</v>
       </c>
       <c r="Q36" s="6"/>
     </row>
     <row r="37" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="141">
+      <c r="A37" s="127">
         <v>35</v>
       </c>
-      <c r="B37" s="55"/>
-      <c r="C37" s="128" t="s">
+      <c r="B37" s="137"/>
+      <c r="C37" s="114" t="s">
         <v>66</v>
       </c>
-      <c r="D37" s="21" t="s">
+      <c r="D37" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="E37" s="21" t="s">
+      <c r="E37" s="19" t="s">
         <v>247</v>
       </c>
-      <c r="F37" s="62" t="s">
+      <c r="F37" s="57" t="s">
         <v>136</v>
       </c>
-      <c r="G37" s="21" t="s">
+      <c r="G37" s="19" t="s">
         <v>219</v>
       </c>
-      <c r="H37" s="52" t="s">
-        <v>250</v>
-      </c>
-      <c r="I37" s="21" t="s">
+      <c r="H37" s="50" t="s">
+        <v>250</v>
+      </c>
+      <c r="I37" s="19" t="s">
         <v>245</v>
       </c>
-      <c r="J37" s="23">
+      <c r="J37" s="21">
         <v>1</v>
       </c>
-      <c r="K37" s="24">
+      <c r="K37" s="22">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L37" s="42" t="s">
+      <c r="L37" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="M37" s="25">
+      <c r="M37" s="23">
         <v>1.36</v>
       </c>
-      <c r="N37" s="67">
+      <c r="N37" s="62">
         <f t="shared" si="2"/>
         <v>1.36</v>
       </c>
-      <c r="O37" s="112">
+      <c r="O37" s="98">
         <v>1.36</v>
       </c>
-      <c r="P37" s="105">
+      <c r="P37" s="92">
         <f t="shared" si="0"/>
         <v>6.8000000000000007</v>
       </c>
       <c r="Q37" s="8"/>
     </row>
-    <row r="38" spans="1:17" s="53" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="141">
+    <row r="38" spans="1:17" s="51" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="127">
         <v>36</v>
       </c>
-      <c r="B38" s="55"/>
-      <c r="C38" s="127" t="s">
+      <c r="B38" s="137"/>
+      <c r="C38" s="113" t="s">
         <v>67</v>
       </c>
-      <c r="D38" s="52" t="s">
+      <c r="D38" s="50" t="s">
         <v>108</v>
       </c>
-      <c r="E38" s="52" t="s">
+      <c r="E38" s="50" t="s">
         <v>246</v>
       </c>
-      <c r="F38" s="26" t="s">
+      <c r="F38" s="24" t="s">
         <v>137</v>
       </c>
-      <c r="G38" s="52" t="s">
+      <c r="G38" s="50" t="s">
         <v>220</v>
       </c>
-      <c r="H38" s="52" t="s">
-        <v>250</v>
-      </c>
-      <c r="I38" s="52" t="s">
+      <c r="H38" s="50" t="s">
+        <v>250</v>
+      </c>
+      <c r="I38" s="50" t="s">
         <v>245</v>
       </c>
-      <c r="J38" s="40">
+      <c r="J38" s="38">
         <v>1</v>
       </c>
-      <c r="K38" s="24">
+      <c r="K38" s="22">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L38" s="42" t="s">
+      <c r="L38" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="M38" s="25">
+      <c r="M38" s="23">
         <v>0.54</v>
       </c>
-      <c r="N38" s="67">
+      <c r="N38" s="62">
         <f t="shared" si="2"/>
         <v>0.54</v>
       </c>
-      <c r="O38" s="112">
+      <c r="O38" s="98">
         <v>0.54</v>
       </c>
-      <c r="P38" s="105">
+      <c r="P38" s="92">
         <f t="shared" si="0"/>
         <v>2.7</v>
       </c>
       <c r="Q38" s="8"/>
     </row>
     <row r="39" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="141">
+      <c r="A39" s="127">
         <v>37</v>
       </c>
-      <c r="B39" s="55"/>
-      <c r="C39" s="128" t="s">
+      <c r="B39" s="137"/>
+      <c r="C39" s="114" t="s">
         <v>68</v>
       </c>
-      <c r="D39" s="21" t="s">
+      <c r="D39" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="E39" s="21" t="s">
+      <c r="E39" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="F39" s="62" t="s">
+      <c r="F39" s="57" t="s">
         <v>171</v>
       </c>
-      <c r="G39" s="21" t="s">
+      <c r="G39" s="19" t="s">
         <v>221</v>
       </c>
-      <c r="H39" s="52" t="s">
-        <v>250</v>
-      </c>
-      <c r="I39" s="21" t="s">
+      <c r="H39" s="50" t="s">
+        <v>250</v>
+      </c>
+      <c r="I39" s="19" t="s">
         <v>245</v>
       </c>
-      <c r="J39" s="23">
+      <c r="J39" s="21">
         <v>1</v>
       </c>
-      <c r="K39" s="24">
+      <c r="K39" s="22">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L39" s="42" t="s">
+      <c r="L39" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="M39" s="25">
+      <c r="M39" s="23">
         <v>4.95</v>
       </c>
-      <c r="N39" s="67">
+      <c r="N39" s="62">
         <f t="shared" si="2"/>
         <v>4.95</v>
       </c>
-      <c r="O39" s="112">
+      <c r="O39" s="98">
         <v>4.95</v>
       </c>
-      <c r="P39" s="105">
+      <c r="P39" s="92">
         <f t="shared" si="0"/>
         <v>24.75</v>
       </c>
       <c r="Q39" s="8"/>
     </row>
     <row r="40" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="141">
+      <c r="A40" s="127">
         <v>38</v>
       </c>
-      <c r="B40" s="55"/>
-      <c r="C40" s="128" t="s">
+      <c r="B40" s="137"/>
+      <c r="C40" s="114" t="s">
         <v>69</v>
       </c>
-      <c r="D40" s="21" t="s">
+      <c r="D40" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="E40" s="21" t="s">
+      <c r="E40" s="19" t="s">
         <v>139</v>
       </c>
-      <c r="F40" s="62" t="s">
+      <c r="F40" s="57" t="s">
         <v>172</v>
       </c>
-      <c r="G40" s="21" t="s">
+      <c r="G40" s="19" t="s">
         <v>222</v>
       </c>
-      <c r="H40" s="52" t="s">
-        <v>250</v>
-      </c>
-      <c r="I40" s="21" t="s">
+      <c r="H40" s="50" t="s">
+        <v>250</v>
+      </c>
+      <c r="I40" s="19" t="s">
         <v>245</v>
       </c>
-      <c r="J40" s="23">
+      <c r="J40" s="21">
         <v>1</v>
       </c>
-      <c r="K40" s="24">
+      <c r="K40" s="22">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L40" s="42" t="s">
+      <c r="L40" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="M40" s="25">
+      <c r="M40" s="23">
         <v>2.74</v>
       </c>
-      <c r="N40" s="67">
+      <c r="N40" s="62">
         <f t="shared" si="2"/>
         <v>2.74</v>
       </c>
-      <c r="O40" s="112">
+      <c r="O40" s="98">
         <v>2.74</v>
       </c>
-      <c r="P40" s="105">
+      <c r="P40" s="92">
         <f t="shared" si="0"/>
         <v>13.700000000000001</v>
       </c>
       <c r="Q40" s="8"/>
     </row>
     <row r="41" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="141">
+      <c r="A41" s="127">
         <v>39</v>
       </c>
-      <c r="B41" s="55"/>
-      <c r="C41" s="128" t="s">
+      <c r="B41" s="137"/>
+      <c r="C41" s="114" t="s">
         <v>253</v>
       </c>
-      <c r="D41" s="21" t="s">
+      <c r="D41" s="19" t="s">
         <v>111</v>
       </c>
-      <c r="E41" s="21" t="s">
+      <c r="E41" s="19" t="s">
         <v>140</v>
       </c>
-      <c r="F41" s="62" t="s">
+      <c r="F41" s="57" t="s">
         <v>173</v>
       </c>
-      <c r="G41" s="23" t="s">
+      <c r="G41" s="21" t="s">
         <v>249</v>
       </c>
-      <c r="H41" s="52" t="s">
-        <v>250</v>
-      </c>
-      <c r="I41" s="21" t="s">
+      <c r="H41" s="50" t="s">
+        <v>250</v>
+      </c>
+      <c r="I41" s="19" t="s">
         <v>245</v>
       </c>
-      <c r="J41" s="23">
+      <c r="J41" s="21">
         <v>1</v>
       </c>
-      <c r="K41" s="24">
+      <c r="K41" s="22">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L41" s="42" t="s">
+      <c r="L41" s="40" t="s">
         <v>239</v>
       </c>
-      <c r="M41" s="25" t="s">
+      <c r="M41" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="N41" s="67" t="e">
+      <c r="N41" s="62" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="O41" s="112" t="s">
+      <c r="O41" s="98" t="s">
         <v>24</v>
       </c>
-      <c r="P41" s="105">
+      <c r="P41" s="92">
         <v>7.34</v>
       </c>
-      <c r="Q41" s="121" t="s">
+      <c r="Q41" s="107" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="42" spans="1:17" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="141">
+      <c r="A42" s="127">
         <v>40</v>
       </c>
-      <c r="B42" s="56"/>
-      <c r="C42" s="131" t="s">
+      <c r="B42" s="138"/>
+      <c r="C42" s="117" t="s">
         <v>71</v>
       </c>
-      <c r="D42" s="30" t="s">
+      <c r="D42" s="28" t="s">
         <v>113</v>
       </c>
-      <c r="E42" s="30" t="s">
+      <c r="E42" s="28" t="s">
         <v>140</v>
       </c>
-      <c r="F42" s="63" t="s">
+      <c r="F42" s="58" t="s">
         <v>174</v>
       </c>
-      <c r="G42" s="30" t="s">
+      <c r="G42" s="28" t="s">
         <v>224</v>
       </c>
-      <c r="H42" s="58" t="s">
-        <v>250</v>
-      </c>
-      <c r="I42" s="30" t="s">
+      <c r="H42" s="53" t="s">
+        <v>250</v>
+      </c>
+      <c r="I42" s="28" t="s">
         <v>245</v>
       </c>
-      <c r="J42" s="31">
+      <c r="J42" s="29">
         <v>1</v>
       </c>
-      <c r="K42" s="32">
+      <c r="K42" s="30">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L42" s="43" t="s">
+      <c r="L42" s="41" t="s">
         <v>239</v>
       </c>
-      <c r="M42" s="33">
+      <c r="M42" s="31">
         <v>0.71</v>
       </c>
-      <c r="N42" s="86">
+      <c r="N42" s="73">
         <f t="shared" si="2"/>
         <v>0.71</v>
       </c>
-      <c r="O42" s="118">
+      <c r="O42" s="104">
         <v>0.71</v>
       </c>
-      <c r="P42" s="108">
+      <c r="P42" s="95">
         <f t="shared" si="0"/>
         <v>3.55</v>
       </c>
       <c r="Q42" s="9"/>
     </row>
     <row r="43" spans="1:17" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="141">
+      <c r="A43" s="127">
         <v>41</v>
       </c>
-      <c r="B43" s="90" t="s">
+      <c r="B43" s="77" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="132" t="s">
+      <c r="C43" s="118" t="s">
         <v>70</v>
       </c>
-      <c r="D43" s="91" t="s">
+      <c r="D43" s="78" t="s">
         <v>112</v>
       </c>
-      <c r="E43" s="91" t="s">
+      <c r="E43" s="78" t="s">
         <v>244</v>
       </c>
-      <c r="F43" s="92" t="s">
+      <c r="F43" s="79" t="s">
         <v>141</v>
       </c>
-      <c r="G43" s="91" t="s">
+      <c r="G43" s="78" t="s">
         <v>223</v>
       </c>
-      <c r="H43" s="93" t="s">
-        <v>250</v>
-      </c>
-      <c r="I43" s="91" t="s">
+      <c r="H43" s="80" t="s">
+        <v>250</v>
+      </c>
+      <c r="I43" s="78" t="s">
         <v>245</v>
       </c>
-      <c r="J43" s="94">
+      <c r="J43" s="81">
         <v>1</v>
       </c>
-      <c r="K43" s="95">
+      <c r="K43" s="82">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L43" s="96" t="s">
+      <c r="L43" s="83" t="s">
         <v>14</v>
       </c>
-      <c r="M43" s="97">
+      <c r="M43" s="84">
         <v>0.73</v>
       </c>
-      <c r="N43" s="98">
+      <c r="N43" s="85">
         <f t="shared" si="2"/>
         <v>0.73</v>
       </c>
-      <c r="O43" s="120">
+      <c r="O43" s="106">
         <v>0.73</v>
       </c>
-      <c r="P43" s="109">
+      <c r="P43" s="96">
         <f t="shared" si="0"/>
         <v>3.65</v>
       </c>
-      <c r="Q43" s="125"/>
+      <c r="Q43" s="111"/>
     </row>
     <row r="44" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="141">
+      <c r="A44" s="127">
         <v>42</v>
       </c>
-      <c r="B44" s="69" t="s">
+      <c r="B44" s="139" t="s">
         <v>228</v>
       </c>
-      <c r="C44" s="126" t="s">
+      <c r="C44" s="112" t="s">
         <v>39</v>
       </c>
-      <c r="D44" s="15" t="s">
+      <c r="D44" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="E44" s="15" t="s">
+      <c r="E44" s="13" t="s">
         <v>244</v>
       </c>
-      <c r="F44" s="61" t="s">
+      <c r="F44" s="56" t="s">
         <v>120</v>
       </c>
-      <c r="G44" s="15" t="s">
+      <c r="G44" s="13" t="s">
         <v>210</v>
       </c>
-      <c r="H44" s="60" t="s">
-        <v>250</v>
-      </c>
-      <c r="I44" s="15" t="s">
+      <c r="H44" s="55" t="s">
+        <v>250</v>
+      </c>
+      <c r="I44" s="13" t="s">
         <v>245</v>
       </c>
-      <c r="J44" s="17">
+      <c r="J44" s="15">
         <v>1</v>
       </c>
-      <c r="K44" s="18">
-        <f>J44*5</f>
+      <c r="K44" s="16">
+        <f t="shared" ref="K44:K49" si="3">J44*5</f>
         <v>5</v>
       </c>
-      <c r="L44" s="41" t="s">
+      <c r="L44" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="M44" s="19">
+      <c r="M44" s="17">
         <v>0.19</v>
       </c>
-      <c r="N44" s="20">
+      <c r="N44" s="18">
         <f>J44*M44</f>
         <v>0.19</v>
       </c>
-      <c r="O44" s="117">
+      <c r="O44" s="103">
         <v>0.19</v>
       </c>
-      <c r="P44" s="104">
+      <c r="P44" s="91">
         <f>O44*K44</f>
         <v>0.95</v>
       </c>
       <c r="Q44" s="6"/>
     </row>
     <row r="45" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="141">
+      <c r="A45" s="127">
         <v>43</v>
       </c>
-      <c r="B45" s="70"/>
-      <c r="C45" s="128" t="s">
+      <c r="B45" s="140"/>
+      <c r="C45" s="114" t="s">
         <v>41</v>
       </c>
-      <c r="D45" s="21" t="s">
+      <c r="D45" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="E45" s="21" t="s">
+      <c r="E45" s="19" t="s">
         <v>244</v>
       </c>
-      <c r="F45" s="62" t="s">
+      <c r="F45" s="57" t="s">
         <v>123</v>
       </c>
-      <c r="G45" s="21" t="s">
+      <c r="G45" s="19" t="s">
         <v>210</v>
       </c>
-      <c r="H45" s="52" t="s">
-        <v>250</v>
-      </c>
-      <c r="I45" s="21" t="s">
+      <c r="H45" s="50" t="s">
+        <v>250</v>
+      </c>
+      <c r="I45" s="19" t="s">
         <v>245</v>
       </c>
-      <c r="J45" s="23">
+      <c r="J45" s="21">
         <v>1</v>
       </c>
-      <c r="K45" s="24">
-        <f>J45*5</f>
+      <c r="K45" s="22">
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="L45" s="42" t="s">
+      <c r="L45" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="M45" s="28">
+      <c r="M45" s="26">
         <v>0.24</v>
       </c>
-      <c r="N45" s="67">
+      <c r="N45" s="62">
         <f>J45*M45</f>
         <v>0.24</v>
       </c>
-      <c r="O45" s="113">
+      <c r="O45" s="99">
         <v>0.24</v>
       </c>
-      <c r="P45" s="105">
+      <c r="P45" s="92">
         <f>O45*K45</f>
         <v>1.2</v>
       </c>
       <c r="Q45" s="8"/>
     </row>
     <row r="46" spans="1:17" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="141">
+      <c r="A46" s="127">
         <v>44</v>
       </c>
-      <c r="B46" s="70"/>
-      <c r="C46" s="128" t="s">
+      <c r="B46" s="140"/>
+      <c r="C46" s="114" t="s">
         <v>42</v>
       </c>
-      <c r="D46" s="21" t="s">
+      <c r="D46" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="E46" s="21" t="s">
+      <c r="E46" s="19" t="s">
         <v>244</v>
       </c>
-      <c r="F46" s="21" t="s">
+      <c r="F46" s="19" t="s">
         <v>124</v>
       </c>
-      <c r="G46" s="21" t="s">
+      <c r="G46" s="19" t="s">
         <v>212</v>
       </c>
-      <c r="H46" s="52" t="s">
-        <v>250</v>
-      </c>
-      <c r="I46" s="21" t="s">
+      <c r="H46" s="50" t="s">
+        <v>250</v>
+      </c>
+      <c r="I46" s="19" t="s">
         <v>245</v>
       </c>
-      <c r="J46" s="23">
+      <c r="J46" s="21">
         <v>1</v>
       </c>
-      <c r="K46" s="24">
-        <f>J46*5</f>
+      <c r="K46" s="22">
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="L46" s="42" t="s">
+      <c r="L46" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="M46" s="28">
+      <c r="M46" s="26">
         <v>1.19</v>
       </c>
-      <c r="N46" s="67">
+      <c r="N46" s="62">
         <f>J46*M46</f>
         <v>1.19</v>
       </c>
-      <c r="O46" s="114">
+      <c r="O46" s="100">
         <v>1.19</v>
       </c>
-      <c r="P46" s="105">
+      <c r="P46" s="92">
         <f>O46*K46</f>
         <v>5.9499999999999993</v>
       </c>
-      <c r="Q46" s="122" t="s">
+      <c r="Q46" s="108" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="47" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="141">
+      <c r="A47" s="127">
         <v>45</v>
       </c>
-      <c r="B47" s="70"/>
-      <c r="C47" s="133" t="s">
+      <c r="B47" s="140"/>
+      <c r="C47" s="119" t="s">
         <v>63</v>
       </c>
-      <c r="D47" s="76" t="s">
+      <c r="D47" s="66" t="s">
         <v>106</v>
       </c>
-      <c r="E47" s="76" t="s">
+      <c r="E47" s="66" t="s">
         <v>244</v>
       </c>
-      <c r="F47" s="76" t="s">
+      <c r="F47" s="66" t="s">
         <v>133</v>
       </c>
-      <c r="G47" s="78" t="s">
-        <v>250</v>
-      </c>
-      <c r="H47" s="78" t="s">
-        <v>250</v>
-      </c>
-      <c r="I47" s="78" t="s">
-        <v>250</v>
-      </c>
-      <c r="J47" s="77">
+      <c r="G47" s="68" t="s">
+        <v>250</v>
+      </c>
+      <c r="H47" s="68" t="s">
+        <v>250</v>
+      </c>
+      <c r="I47" s="68" t="s">
+        <v>250</v>
+      </c>
+      <c r="J47" s="67">
         <v>2</v>
       </c>
-      <c r="K47" s="79">
-        <f>J47*5</f>
+      <c r="K47" s="69">
+        <f t="shared" si="3"/>
         <v>10</v>
       </c>
-      <c r="L47" s="78" t="s">
-        <v>250</v>
-      </c>
-      <c r="M47" s="78" t="s">
-        <v>250</v>
-      </c>
-      <c r="N47" s="78" t="s">
-        <v>250</v>
-      </c>
-      <c r="O47" s="78" t="s">
-        <v>250</v>
-      </c>
-      <c r="P47" s="78" t="s">
-        <v>250</v>
-      </c>
-      <c r="Q47" s="123" t="s">
+      <c r="L47" s="68" t="s">
+        <v>250</v>
+      </c>
+      <c r="M47" s="68" t="s">
+        <v>250</v>
+      </c>
+      <c r="N47" s="68" t="s">
+        <v>250</v>
+      </c>
+      <c r="O47" s="68" t="s">
+        <v>250</v>
+      </c>
+      <c r="P47" s="68" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q47" s="109" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="48" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="141">
+      <c r="A48" s="127">
         <v>46</v>
       </c>
-      <c r="B48" s="70"/>
-      <c r="C48" s="75" t="s">
+      <c r="B48" s="140"/>
+      <c r="C48" s="65" t="s">
         <v>255</v>
       </c>
-      <c r="D48" s="76" t="s">
+      <c r="D48" s="66" t="s">
         <v>85</v>
       </c>
-      <c r="E48" s="76" t="s">
+      <c r="E48" s="66" t="s">
         <v>244</v>
       </c>
-      <c r="F48" s="76" t="s">
+      <c r="F48" s="66" t="s">
         <v>121</v>
       </c>
-      <c r="G48" s="78" t="s">
-        <v>250</v>
-      </c>
-      <c r="H48" s="78" t="s">
-        <v>250</v>
-      </c>
-      <c r="I48" s="78" t="s">
-        <v>250</v>
-      </c>
-      <c r="J48" s="77">
+      <c r="G48" s="68" t="s">
+        <v>250</v>
+      </c>
+      <c r="H48" s="68" t="s">
+        <v>250</v>
+      </c>
+      <c r="I48" s="68" t="s">
+        <v>250</v>
+      </c>
+      <c r="J48" s="67">
         <v>1</v>
       </c>
-      <c r="K48" s="79">
-        <f>J48*5</f>
+      <c r="K48" s="69">
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="L48" s="78" t="s">
-        <v>250</v>
-      </c>
-      <c r="M48" s="78" t="s">
-        <v>250</v>
-      </c>
-      <c r="N48" s="78" t="s">
-        <v>250</v>
-      </c>
-      <c r="O48" s="78" t="s">
-        <v>250</v>
-      </c>
-      <c r="P48" s="78" t="s">
-        <v>250</v>
-      </c>
-      <c r="Q48" s="123" t="s">
+      <c r="L48" s="68" t="s">
+        <v>250</v>
+      </c>
+      <c r="M48" s="68" t="s">
+        <v>250</v>
+      </c>
+      <c r="N48" s="68" t="s">
+        <v>250</v>
+      </c>
+      <c r="O48" s="68" t="s">
+        <v>250</v>
+      </c>
+      <c r="P48" s="68" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q48" s="109" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="49" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="141">
+      <c r="A49" s="127">
         <v>47</v>
       </c>
-      <c r="B49" s="71"/>
-      <c r="C49" s="134" t="s">
+      <c r="B49" s="141"/>
+      <c r="C49" s="120" t="s">
         <v>40</v>
       </c>
-      <c r="D49" s="99" t="s">
+      <c r="D49" s="86" t="s">
         <v>86</v>
       </c>
-      <c r="E49" s="99" t="s">
+      <c r="E49" s="86" t="s">
         <v>244</v>
       </c>
-      <c r="F49" s="99" t="s">
+      <c r="F49" s="86" t="s">
         <v>122</v>
       </c>
-      <c r="G49" s="99" t="s">
+      <c r="G49" s="86" t="s">
         <v>211</v>
       </c>
-      <c r="H49" s="100" t="s">
-        <v>250</v>
-      </c>
-      <c r="I49" s="99" t="s">
-        <v>250</v>
-      </c>
-      <c r="J49" s="101">
+      <c r="H49" s="87" t="s">
+        <v>250</v>
+      </c>
+      <c r="I49" s="86" t="s">
+        <v>250</v>
+      </c>
+      <c r="J49" s="88">
         <v>1</v>
       </c>
-      <c r="K49" s="102">
-        <f>J49*5</f>
+      <c r="K49" s="89">
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="L49" s="99" t="s">
-        <v>250</v>
-      </c>
-      <c r="M49" s="99" t="s">
-        <v>250</v>
-      </c>
-      <c r="N49" s="99" t="s">
-        <v>250</v>
-      </c>
-      <c r="O49" s="99" t="s">
-        <v>250</v>
-      </c>
-      <c r="P49" s="99" t="s">
-        <v>250</v>
-      </c>
-      <c r="Q49" s="124" t="s">
+      <c r="L49" s="86" t="s">
+        <v>250</v>
+      </c>
+      <c r="M49" s="86" t="s">
+        <v>250</v>
+      </c>
+      <c r="N49" s="86" t="s">
+        <v>250</v>
+      </c>
+      <c r="O49" s="86" t="s">
+        <v>250</v>
+      </c>
+      <c r="P49" s="86" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q49" s="110" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="50" spans="1:17" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="5"/>
       <c r="B50" s="5"/>
-      <c r="C50" s="135"/>
+      <c r="C50" s="121"/>
       <c r="D50" s="5"/>
       <c r="E50" s="5"/>
       <c r="F50" s="5"/>
       <c r="G50" s="5"/>
       <c r="H50" s="5"/>
       <c r="I50"/>
-      <c r="J50" s="14" t="s">
+      <c r="J50" s="133" t="s">
         <v>7</v>
       </c>
-      <c r="K50" s="14"/>
-      <c r="L50" s="14"/>
-      <c r="M50" s="14"/>
+      <c r="K50" s="133"/>
+      <c r="L50" s="133"/>
+      <c r="M50" s="133"/>
       <c r="N50" s="2"/>
       <c r="O50" s="5"/>
       <c r="P50" s="3">
@@ -4704,25 +4719,25 @@
     <row r="51" spans="1:17" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A51" s="5"/>
       <c r="B51" s="5"/>
-      <c r="C51" s="135"/>
+      <c r="C51" s="121"/>
       <c r="D51" s="5"/>
       <c r="E51" s="5"/>
       <c r="F51" s="5"/>
       <c r="G51" s="5"/>
       <c r="H51" s="5"/>
       <c r="I51"/>
-      <c r="J51" s="13" t="s">
+      <c r="J51" s="128" t="s">
         <v>11</v>
       </c>
-      <c r="K51" s="13"/>
-      <c r="L51" s="13"/>
-      <c r="M51" s="13"/>
+      <c r="K51" s="128"/>
+      <c r="L51" s="128"/>
+      <c r="M51" s="128"/>
       <c r="N51" s="4">
         <f>SUM(N3:N16)</f>
         <v>9.4210000000000012</v>
       </c>
       <c r="O51" s="5"/>
-      <c r="P51" s="5">
+      <c r="P51" s="142">
         <f>P50/5</f>
         <v>7.0718000000000005</v>
       </c>
